--- a/docs/olap/Senior Care Management - Seed Specification.xlsx
+++ b/docs/olap/Senior Care Management - Seed Specification.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Counts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visit Distribution" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Volume" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Senior Demographics" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query Test Scenarios" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Validation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Entity Counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Visit Distribution" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly Volume" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Senior Demographics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Query Test Scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Data Validation" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -958,7 +961,7 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>VisitStatus not Cancelled; both timestamps present; check-in &gt; scheduled start + 10 minutes.</t>
+          <t>VisitStatus not Cancelled; both timestamps present; check-in &gt; scheduled start + 10 minutes and &lt;= scheduled start + 60 minutes.</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
@@ -983,12 +986,12 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Non-cancelled; explicit VisitStatus = Missed OR no check-in by 60 minutes after scheduled start once cutoff has elapsed.</t>
+          <t>Scheduled start + 60 minutes is in the past, and either Status = Scheduled with no check-in, or Status = Completed with check-in after scheduled start + 60 minutes.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>A late check-in after 60 minutes does not clear missed. Future/pending visits are not marked missed prematurely.</t>
+          <t>Missed is computed, never a Status value. A check-in after 60 minutes does not clear it, and Completed does not prevent it.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1016,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Cancelled visits excluded from missed percentage denominator, pending Query 1 contract confirmation.</t>
+          <t>Excluded from VisitCount and MissedCount (Query1-Contract.md).</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1041,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Synthetic distribution; confirm status vocabulary against OLTP.</t>
+          <t>Synthetic distribution.</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1310,25 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Volumes include cancelled visits. Query 1 VisitCount for a month is that month's volume minus its cancelled visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>The months above map in order onto the 15 months ending at seed time (2025-01 is the oldest, 2026-03 the current month). The current month's volume is scaled to its elapsed days, then all months are scaled so the total stays 3,000. If seeding runs on the 1st, the 15 months end with the previous month.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1775,7 +1796,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>15 monthly buckets from 2025-01 through 2026-03; sum scheduled visits=3,000.</t>
+          <t>15 monthly buckets of history visits ending at seed time; sum scheduled history visits=3,000.</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -1885,7 +1906,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Age computed from DateOfBirth at moving anchor date; labels Under 65, 65-74, 75-84, 85+.</t>
+          <t>Not Cancelled, and no check-in at or before +60 once +60 has passed. Status is never Missed; a check-in after +60 does not clear it; not yet due visits are not Missed.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1907,12 +1928,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Exactly S001-S005 have &gt;=3 missed visits in the 90-day window; window endpoints included.</t>
+          <t>Age computed at the anchor date and falls into Under 65, 65-74, 75-84, or 85+.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>All three bands represented.</t>
+          <t>All four bands represented.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1929,12 +1950,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>S006/S007 excluded; S007 earliest miss is outside the window.</t>
+          <t>Seniors with &gt;=3 missed visits in the 90 days before the anchor date, both ends included.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>S001–S005 qualify.</t>
+          <t>Exactly S001-S005 qualify.</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1951,12 +1972,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>C030 has no Late visits and one post-60 Missed visit.</t>
+          <t>S006 and S007 have &lt;3 missed visits inside the window.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>S006–S007 excluded.</t>
+          <t>S006-S007 excluded.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1968,44 +1989,44 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Time of day</t>
+          <t>Query 3 zero-late caregiver</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Anchor is latest passed, non-cancelled scheduled start; future demo visits move it forward.</t>
+          <t>C030 has only on-time visits plus one check-in after +60, so no Late visits.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>No unmapped times after approval.</t>
+          <t>C030 absent from OLAP-2.</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Service category</t>
+          <t>Anchor date</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>ServiceCategory populated only from an approved mapping, never inferred automatically from Description.</t>
+          <t>The anchor is the latest passed, non-cancelled scheduled start. Future demo visits exist, so it moves forward as they pass.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>No unapproved category inference.</t>
+          <t>Anchor date is at or just before the current date.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
